--- a/reports/VIC_202606.xlsx
+++ b/reports/VIC_202606.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Per-Entry Detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Breakdown'!$A$1:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Breakdown'!$A$1:$S$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Per-Entry Detail'!$A$2:$V$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -153,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,10 +233,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -604,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -614,7 +610,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
@@ -779,7 +775,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-22 20:47:00</t>
+          <t>2026-06-22 22:07:00</t>
         </is>
       </c>
     </row>
@@ -799,7 +795,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$13,959.50</t>
+          <t>$13,949.76</t>
         </is>
       </c>
     </row>
@@ -811,7 +807,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$459.50</t>
+          <t>$449.76</t>
         </is>
       </c>
     </row>
@@ -823,7 +819,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$456.20</t>
+          <t>$445.98</t>
         </is>
       </c>
     </row>
@@ -835,7 +831,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$3.30</t>
+          <t>$3.78</t>
         </is>
       </c>
     </row>
@@ -847,7 +843,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+3.40%</t>
+          <t>+3.33%</t>
         </is>
       </c>
     </row>
@@ -881,7 +877,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5 / 2</t>
+          <t>5 / 3</t>
         </is>
       </c>
     </row>
@@ -893,7 +889,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>71.43%</t>
+          <t>62.50%</t>
         </is>
       </c>
     </row>
@@ -989,254 +985,239 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Total entries</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B36" s="3" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="38"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Risk:Reward (executed)</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Risk:Reward (executed)</t>
-        </is>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Filled entries</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Filled entries</t>
+          <t>No-fill entries</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>No-fill entries</t>
+          <t>Winning entries</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Winning entries</t>
+          <t>Losing entries</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Losing entries</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>20</v>
+          <t>Avg planned R:R</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1:2.7</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Avg planned R:R</t>
+          <t>Avg realized R</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1:2.7</t>
+          <t>1:0.22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Avg realized R</t>
+          <t>Payoff (avg win / avg loss)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1:0.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Payoff (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1:0.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
+          <t>1:0.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Breakdown</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Monthly Breakdown</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Signals</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Losses</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>No-fills</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Win rate</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Trading P&amp;L</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Closed lots</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Net P&amp;L</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Equity EoM</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Regime</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Signals</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Wins</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Losses</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>No-fills</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Win rate</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>Trading P&amp;L</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>Bonus</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>Closed lots</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>Net P&amp;L</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="inlineStr">
-        <is>
-          <t>Equity EoM</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>R4parab</t>
         </is>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C49" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="D49" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E50" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F50" s="9" t="n">
+      <c r="E49" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="n">
-        <v>456.2000000000007</v>
-      </c>
-      <c r="I50" s="10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J50" s="11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K50" s="10" t="n">
-        <v>459.5000000000008</v>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>+3.40%</t>
-        </is>
-      </c>
-      <c r="M50" s="13" t="n">
-        <v>13959.5</v>
+      <c r="F49" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>445.9771428571457</v>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>449.7571428571458</v>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>+3.33%</t>
+        </is>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>13949.75714285714</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A47:M47"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1249,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1261,17 +1242,16 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1322,55 +1302,50 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Entries</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Entries</t>
+          <t>Avg R:R</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
-          <t>Avg R:R</t>
+          <t>Avg R</t>
         </is>
       </c>
       <c r="M1" s="4" t="inlineStr">
         <is>
-          <t>Avg R</t>
+          <t>Trading P&amp;L</t>
         </is>
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
-          <t>Trading P&amp;L</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="O1" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Closed lots</t>
         </is>
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>Closed lots</t>
+          <t>Net P&amp;L</t>
         </is>
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
-          <t>Net P&amp;L</t>
+          <t>P&amp;L %</t>
         </is>
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>P&amp;L %</t>
+          <t>Equity EoD</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>Equity EoD</t>
-        </is>
-      </c>
-      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Drawdown %</t>
         </is>
@@ -1389,7 +1364,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="9" t="n">
         <v>25</v>
@@ -1404,52 +1379,49 @@
         <v>14</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" s="9" t="n">
         <v>88</v>
       </c>
-      <c r="L2" s="14" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>1:2.7</t>
         </is>
       </c>
-      <c r="M2" s="15" t="inlineStr">
-        <is>
-          <t>1:0.21</t>
-        </is>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>1:0.22</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="n">
+        <v>445.9771428571457</v>
       </c>
       <c r="N2" s="10" t="n">
-        <v>456.2000000000007</v>
-      </c>
-      <c r="O2" s="10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P2" s="11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q2" s="10" t="n">
-        <v>459.5000000000008</v>
-      </c>
-      <c r="R2" s="12" t="inlineStr">
-        <is>
-          <t>+3.40%</t>
-        </is>
-      </c>
-      <c r="S2" s="13" t="n">
-        <v>13959.5</v>
-      </c>
-      <c r="T2" s="9" t="inlineStr">
+        <v>3.78</v>
+      </c>
+      <c r="O2" s="11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P2" s="10" t="n">
+        <v>449.7571428571458</v>
+      </c>
+      <c r="Q2" s="12" t="inlineStr">
+        <is>
+          <t>+3.33%</t>
+        </is>
+      </c>
+      <c r="R2" s="13" t="n">
+        <v>13949.75714285714</v>
+      </c>
+      <c r="S2" s="9" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T2"/>
+  <autoFilter ref="A1:S2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8685,7 +8657,7 @@
       </c>
       <c r="P87" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TIME_EXIT</t>
         </is>
       </c>
       <c r="Q87" s="8" t="inlineStr">
@@ -8693,15 +8665,27 @@
           <t>2026-06-22 18:39</t>
         </is>
       </c>
-      <c r="R87" s="8" t="n"/>
-      <c r="S87" s="42" t="n"/>
-      <c r="T87" s="47" t="n"/>
+      <c r="R87" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:35</t>
+        </is>
+      </c>
+      <c r="S87" s="42" t="n">
+        <v>4187.39</v>
+      </c>
+      <c r="T87" s="44" t="n">
+        <v>8.208571428571304</v>
+      </c>
       <c r="U87" s="45" t="inlineStr">
         <is>
           <t>1:2.8</t>
         </is>
       </c>
-      <c r="V87" s="48" t="n"/>
+      <c r="V87" s="46" t="inlineStr">
+        <is>
+          <t>1:0.28</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="25" t="inlineStr">
@@ -8761,7 +8745,7 @@
       </c>
       <c r="P88" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TIME_EXIT</t>
         </is>
       </c>
       <c r="Q88" s="8" t="inlineStr">
@@ -8769,15 +8753,27 @@
           <t>2026-06-22 18:39</t>
         </is>
       </c>
-      <c r="R88" s="8" t="n"/>
-      <c r="S88" s="42" t="n"/>
-      <c r="T88" s="47" t="n"/>
+      <c r="R88" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:35</t>
+        </is>
+      </c>
+      <c r="S88" s="42" t="n">
+        <v>4187.39</v>
+      </c>
+      <c r="T88" s="44" t="n">
+        <v>10.06571428571442</v>
+      </c>
       <c r="U88" s="45" t="inlineStr">
         <is>
           <t>1:2.9</t>
         </is>
       </c>
-      <c r="V88" s="48" t="n"/>
+      <c r="V88" s="46" t="inlineStr">
+        <is>
+          <t>1:0.34</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="25" t="inlineStr">
@@ -8837,7 +8833,7 @@
       </c>
       <c r="P89" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TIME_EXIT</t>
         </is>
       </c>
       <c r="Q89" s="8" t="inlineStr">
@@ -8845,15 +8841,27 @@
           <t>2026-06-22 18:39</t>
         </is>
       </c>
-      <c r="R89" s="8" t="n"/>
-      <c r="S89" s="42" t="n"/>
-      <c r="T89" s="47" t="n"/>
+      <c r="R89" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:35</t>
+        </is>
+      </c>
+      <c r="S89" s="42" t="n">
+        <v>4187.39</v>
+      </c>
+      <c r="T89" s="44" t="n">
+        <v>11.92285714285754</v>
+      </c>
       <c r="U89" s="45" t="inlineStr">
         <is>
           <t>1:3.0</t>
         </is>
       </c>
-      <c r="V89" s="48" t="n"/>
+      <c r="V89" s="46" t="inlineStr">
+        <is>
+          <t>1:0.41</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="25" t="inlineStr">
@@ -8913,7 +8921,7 @@
       </c>
       <c r="P90" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TIME_EXIT</t>
         </is>
       </c>
       <c r="Q90" s="8" t="inlineStr">
@@ -8921,15 +8929,27 @@
           <t>2026-06-22 18:45</t>
         </is>
       </c>
-      <c r="R90" s="8" t="n"/>
-      <c r="S90" s="42" t="n"/>
-      <c r="T90" s="47" t="n"/>
+      <c r="R90" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:35</t>
+        </is>
+      </c>
+      <c r="S90" s="42" t="n">
+        <v>4187.39</v>
+      </c>
+      <c r="T90" s="44" t="n">
+        <v>13.78000000000065</v>
+      </c>
       <c r="U90" s="45" t="inlineStr">
         <is>
           <t>1:3.0</t>
         </is>
       </c>
-      <c r="V90" s="48" t="n"/>
+      <c r="V90" s="46" t="inlineStr">
+        <is>
+          <t>1:0.47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:V90"/>
